--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>17316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>37528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48724</t>
+          <t>49097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80525</t>
+          <t>82040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72375</t>
+          <t>73000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110356</t>
+          <t>109472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664937</t>
+          <t>665941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685790</t>
+          <t>686153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616525</t>
+          <t>615010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>648326</t>
+          <t>647953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1290163</t>
+          <t>1291047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1328144</t>
+          <t>1327519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23149</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47361</t>
+          <t>48069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73167</t>
+          <t>73015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110838</t>
+          <t>110913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104038</t>
+          <t>104120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145620</t>
+          <t>149563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>970586</t>
+          <t>969878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>994798</t>
+          <t>993906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>921346</t>
+          <t>921271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959017</t>
+          <t>959169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1904511</t>
+          <t>1900568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1946093</t>
+          <t>1946011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40612</t>
+          <t>41698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49395</t>
+          <t>49971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80121</t>
+          <t>80562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74890</t>
+          <t>75076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113693</t>
+          <t>115965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717011</t>
+          <t>715925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739127</t>
+          <t>739169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697053</t>
+          <t>696612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>727779</t>
+          <t>727203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1421104</t>
+          <t>1418832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1459907</t>
+          <t>1459721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47475</t>
+          <t>48495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91164</t>
+          <t>91233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133153</t>
+          <t>132966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122458</t>
+          <t>123951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171765</t>
+          <t>171462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900264</t>
+          <t>899244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>924485</t>
+          <t>923769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>918748</t>
+          <t>918935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960737</t>
+          <t>960668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1827875</t>
+          <t>1828178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1877182</t>
+          <t>1875689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145479</t>
+          <t>147553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>293090</t>
+          <t>296365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366377</t>
+          <t>365898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409542</t>
+          <t>410937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>495356</t>
+          <t>492949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3281300</t>
+          <t>3279226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3326902</t>
+          <t>3326871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3191932</t>
+          <t>3192411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3265219</t>
+          <t>3261944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6489732</t>
+          <t>6492139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6575546</t>
+          <t>6574151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53925</t>
+          <t>53884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86992</t>
+          <t>84133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73587</t>
+          <t>72279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110272</t>
+          <t>109597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>642501</t>
+          <t>641589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>661443</t>
+          <t>660386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585847</t>
+          <t>588706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618914</t>
+          <t>618955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1237367</t>
+          <t>1238042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1274052</t>
+          <t>1275360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20605</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42910</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67283</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>108431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93864</t>
+          <t>94277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137141</t>
+          <t>140581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>979521</t>
+          <t>981338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1001826</t>
+          <t>1001793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>936537</t>
+          <t>934482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>975630</t>
+          <t>974146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1928203</t>
+          <t>1924763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1971480</t>
+          <t>1971067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>33446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46233</t>
+          <t>46920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78370</t>
+          <t>78003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65316</t>
+          <t>64455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101886</t>
+          <t>101548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>727164</t>
+          <t>726106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>746429</t>
+          <t>745328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>706641</t>
+          <t>707008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>738778</t>
+          <t>738091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1442677</t>
+          <t>1443015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1479247</t>
+          <t>1480108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>47969</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84013</t>
+          <t>84092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124323</t>
+          <t>126192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113972</t>
+          <t>113650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163751</t>
+          <t>161732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>892221</t>
+          <t>889598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915637</t>
+          <t>914228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919456</t>
+          <t>917587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959766</t>
+          <t>959687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1817595</t>
+          <t>1819614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1867374</t>
+          <t>1867696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85975</t>
+          <t>87899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>127715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>281573</t>
+          <t>284649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>356245</t>
+          <t>358179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380773</t>
+          <t>382863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>462015</t>
+          <t>464351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3267103</t>
+          <t>3266635</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3308375</t>
+          <t>3306451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3188297</t>
+          <t>3186363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3262969</t>
+          <t>3259893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6476877</t>
+          <t>6474541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6558119</t>
+          <t>6556029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45306</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70683</t>
+          <t>71294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90096</t>
+          <t>90910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130798</t>
+          <t>131030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146130</t>
+          <t>149450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192640</t>
+          <t>191451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564758</t>
+          <t>564147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>590135</t>
+          <t>589965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>594532</t>
+          <t>594300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>635234</t>
+          <t>634420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1168132</t>
+          <t>1169321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1214642</t>
+          <t>1211322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86550</t>
+          <t>85957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123944</t>
+          <t>122540</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>155770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136454</t>
+          <t>135459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>235785</t>
+          <t>236472</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1106314</t>
+          <t>1106907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1158959</t>
+          <t>1162648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>802214</t>
+          <t>802881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>834707</t>
+          <t>836111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1915731</t>
+          <t>1915044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2015062</t>
+          <t>2016057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33850</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59010</t>
+          <t>61007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>46294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126249</t>
+          <t>125206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88058</t>
+          <t>94218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163764</t>
+          <t>168106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645670</t>
+          <t>643673</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670830</t>
+          <t>670439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>807117</t>
+          <t>808160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>883628</t>
+          <t>887072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1474282</t>
+          <t>1469940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1549988</t>
+          <t>1543828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50196</t>
+          <t>50730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78941</t>
+          <t>78470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138128</t>
+          <t>139164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>196730</t>
+          <t>199102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206592</t>
+          <t>201938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266042</t>
+          <t>262928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>847890</t>
+          <t>848361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876635</t>
+          <t>876101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898202</t>
+          <t>895830</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>956804</t>
+          <t>955768</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1755721</t>
+          <t>1758835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1815171</t>
+          <t>1819825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>178838</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>261829</t>
+          <t>263678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>417804</t>
+          <t>413012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>567954</t>
+          <t>567137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>652587</t>
+          <t>650438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>812477</t>
+          <t>818617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3197988</t>
+          <t>3196139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3281223</t>
+          <t>3280979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3144326</t>
+          <t>3145143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3294476</t>
+          <t>3299268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6359620</t>
+          <t>6353480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6519510</t>
+          <t>6521659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>39303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>47949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82040</t>
+          <t>80148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>72370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109472</t>
+          <t>109019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665941</t>
+          <t>664166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686153</t>
+          <t>686263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>615010</t>
+          <t>616902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647953</t>
+          <t>649101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1291047</t>
+          <t>1291500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1327519</t>
+          <t>1328149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48069</t>
+          <t>46960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73015</t>
+          <t>73155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110913</t>
+          <t>110021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104120</t>
+          <t>105253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149563</t>
+          <t>149246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>969878</t>
+          <t>970987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993906</t>
+          <t>993900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>921271</t>
+          <t>922163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959169</t>
+          <t>959029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1900568</t>
+          <t>1900885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1946011</t>
+          <t>1944878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41698</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49971</t>
+          <t>50692</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80562</t>
+          <t>81357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75076</t>
+          <t>75204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115965</t>
+          <t>112332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>715925</t>
+          <t>716932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739169</t>
+          <t>739252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>696612</t>
+          <t>695817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>727203</t>
+          <t>726482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1418832</t>
+          <t>1422465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1459721</t>
+          <t>1459593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48495</t>
+          <t>49999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91233</t>
+          <t>91398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132966</t>
+          <t>131569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123951</t>
+          <t>122163</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171462</t>
+          <t>169540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>899244</t>
+          <t>897740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923769</t>
+          <t>924124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>918935</t>
+          <t>920332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960668</t>
+          <t>960503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1828178</t>
+          <t>1830100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1875689</t>
+          <t>1877477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>101165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147553</t>
+          <t>149257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296365</t>
+          <t>297365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>365898</t>
+          <t>371449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410937</t>
+          <t>412347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>492949</t>
+          <t>497420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3279226</t>
+          <t>3277522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3326871</t>
+          <t>3325614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3192411</t>
+          <t>3186860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3261944</t>
+          <t>3260944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6492139</t>
+          <t>6487668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6574151</t>
+          <t>6572741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33211</t>
+          <t>32065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53884</t>
+          <t>52693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84133</t>
+          <t>84575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72279</t>
+          <t>73084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109597</t>
+          <t>110569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641589</t>
+          <t>642735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660386</t>
+          <t>660287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>588706</t>
+          <t>588264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618955</t>
+          <t>620146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1238042</t>
+          <t>1237070</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1275360</t>
+          <t>1274555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41093</t>
+          <t>41926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>65974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108431</t>
+          <t>105192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94277</t>
+          <t>95251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140581</t>
+          <t>140117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>981338</t>
+          <t>980505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1001793</t>
+          <t>1001799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>934482</t>
+          <t>937721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>974146</t>
+          <t>976939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1924763</t>
+          <t>1925227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1971067</t>
+          <t>1970093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33446</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78003</t>
+          <t>79512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64455</t>
+          <t>66201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>102368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726106</t>
+          <t>727050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>745328</t>
+          <t>745894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>707008</t>
+          <t>705499</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>738091</t>
+          <t>739200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1443015</t>
+          <t>1442195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1480108</t>
+          <t>1478362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47969</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84092</t>
+          <t>83382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126192</t>
+          <t>125142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113650</t>
+          <t>113896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161732</t>
+          <t>161314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>889598</t>
+          <t>892450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914228</t>
+          <t>914220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>917587</t>
+          <t>918637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959687</t>
+          <t>960397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1819614</t>
+          <t>1820032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1867696</t>
+          <t>1867450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87899</t>
+          <t>85097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127715</t>
+          <t>129311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>284649</t>
+          <t>281670</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>358179</t>
+          <t>355091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>382863</t>
+          <t>383156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>464351</t>
+          <t>466397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3266635</t>
+          <t>3265039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3306451</t>
+          <t>3309253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3186363</t>
+          <t>3189451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3259893</t>
+          <t>3262872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6474541</t>
+          <t>6472495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6556029</t>
+          <t>6555736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57440</t>
+          <t>60978</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>47668</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71294</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>114054</t>
+          <t>121706</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90910</t>
+          <t>107251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131030</t>
+          <t>137922</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>171494</t>
+          <t>182684</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149450</t>
+          <t>163722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191451</t>
+          <t>204374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>578001</t>
+          <t>629732</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564147</t>
+          <t>614284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>589965</t>
+          <t>643042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>611276</t>
+          <t>612474</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>594300</t>
+          <t>596258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>634420</t>
+          <t>626929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1189278</t>
+          <t>1242205</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1169321</t>
+          <t>1220515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1211322</t>
+          <t>1261167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>67438</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>53509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>82296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>139200</t>
+          <t>151950</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>134342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155770</t>
+          <t>171005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>202577</t>
+          <t>219388</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>196476</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236472</t>
+          <t>245345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1129488</t>
+          <t>981479</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1106907</t>
+          <t>966621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1162648</t>
+          <t>995408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>819451</t>
+          <t>919524</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>802881</t>
+          <t>900469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>836111</t>
+          <t>937132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1948939</t>
+          <t>1901003</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1915044</t>
+          <t>1875046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2016057</t>
+          <t>1923915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45947</t>
+          <t>50837</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>38789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61007</t>
+          <t>66681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>104866</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46294</t>
+          <t>88365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125206</t>
+          <t>120589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>137992</t>
+          <t>155704</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>136262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168106</t>
+          <t>179216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>658733</t>
+          <t>752236</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643673</t>
+          <t>736392</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670439</t>
+          <t>764284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>841322</t>
+          <t>707393</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>808160</t>
+          <t>691670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>887072</t>
+          <t>723894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1500054</t>
+          <t>1459628</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1469940</t>
+          <t>1436116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1543828</t>
+          <t>1479070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>67448</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50730</t>
+          <t>54331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78470</t>
+          <t>82027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>172295</t>
+          <t>183144</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139164</t>
+          <t>164225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199102</t>
+          <t>204378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>236063</t>
+          <t>250592</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>201938</t>
+          <t>225286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262928</t>
+          <t>276828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>863064</t>
+          <t>922614</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848361</t>
+          <t>908035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876101</t>
+          <t>935731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>922637</t>
+          <t>935897</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>895830</t>
+          <t>914663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>955768</t>
+          <t>954816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1785700</t>
+          <t>1858512</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1758835</t>
+          <t>1832276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1819825</t>
+          <t>1883818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>230531</t>
+          <t>246701</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178838</t>
+          <t>219051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>263678</t>
+          <t>273162</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>517594</t>
+          <t>561666</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>413012</t>
+          <t>526629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>567137</t>
+          <t>597294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>748125</t>
+          <t>808367</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>650438</t>
+          <t>762491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>818617</t>
+          <t>855960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3229286</t>
+          <t>3286061</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3196139</t>
+          <t>3259600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3280979</t>
+          <t>3313711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3194686</t>
+          <t>3175288</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3145143</t>
+          <t>3139660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3299268</t>
+          <t>3210325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6423972</t>
+          <t>6461349</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6353480</t>
+          <t>6413756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6521659</t>
+          <t>6507225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
